--- a/files/UAE_007_ФПЗ_ПРЕДВАРИТЕЛЬНЫЙ.xlsx
+++ b/files/UAE_007_ФПЗ_ПРЕДВАРИТЕЛЬНЫЙ.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinov\OneDrive\Desktop\РАБОЧАЯ\001 ИМПОРТ\001 containers\2026\UAE\UAE#7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinov\OneDrive\Desktop\РАБОЧАЯ\001 ИМПОРТ\001 containers\2026\001 UAE\UAE#7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146AB5E2-E570-4228-B552-C2416DFEE876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25742DA-F003-4C2F-BC6C-0E3A581BFDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="1845" windowWidth="35295" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ФПЗ_Э7" sheetId="1" r:id="rId1"/>
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="29">
-        <f t="shared" ref="T3:T5" si="14">P3+Q3+R3+S3</f>
+        <f t="shared" ref="T3:T4" si="14">P3+Q3+R3+S3</f>
         <v>0</v>
       </c>
       <c r="U3" s="30" t="str">
@@ -5232,7 +5232,7 @@
         <v>35.655189873417719</v>
       </c>
       <c r="L5" s="27">
-        <f t="shared" si="1"/>
+        <f>K5*E5</f>
         <v>8557.2455696202524</v>
       </c>
       <c r="M5" s="28">
@@ -5259,15 +5259,15 @@
         <v>87490.406753645439</v>
       </c>
       <c r="S5" s="29">
-        <f t="shared" si="7"/>
+        <f>$S$13/$M$11*M5</f>
         <v>1841.9033000767463</v>
       </c>
       <c r="T5" s="29">
-        <f t="shared" si="14"/>
+        <f>P5+Q5+R5+S5</f>
         <v>968161.430053722</v>
       </c>
       <c r="U5" s="30">
-        <f t="shared" si="9"/>
+        <f>IFERROR(SUM(T5/E5),"")</f>
         <v>4034.0059585571748</v>
       </c>
       <c r="V5" s="31">
@@ -6296,7 +6296,9 @@
       <c r="D6" s="26">
         <v>1</v>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="26">
+        <v>0</v>
+      </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
       <c r="H6" s="26">
@@ -9658,7 +9660,9 @@
       <c r="T14" s="5"/>
     </row>
     <row r="15" spans="1:1022" x14ac:dyDescent="0.2">
-      <c r="L15" s="6"/>
+      <c r="L15" s="6">
+        <v>8557.2455696202524</v>
+      </c>
       <c r="M15" s="6"/>
       <c r="N15" s="5"/>
       <c r="Q15" s="5"/>
@@ -9667,7 +9671,9 @@
       <c r="T15" s="5"/>
     </row>
     <row r="16" spans="1:1022" x14ac:dyDescent="0.2">
-      <c r="L16" s="6"/>
+      <c r="L16" s="6">
+        <v>1768</v>
+      </c>
       <c r="M16" s="6"/>
       <c r="N16" s="5"/>
       <c r="Q16" s="5"/>
@@ -9694,6 +9700,10 @@
       <c r="T18" s="5"/>
     </row>
     <row r="19" spans="12:20" x14ac:dyDescent="0.2">
+      <c r="L19" s="7">
+        <f>+SUM(L15:L16)</f>
+        <v>10325.245569620252</v>
+      </c>
       <c r="N19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
@@ -9708,6 +9718,9 @@
       <c r="T20" s="5"/>
     </row>
     <row r="21" spans="12:20" x14ac:dyDescent="0.2">
+      <c r="L21" s="7">
+        <v>10325.245569620252</v>
+      </c>
       <c r="N21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
